--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Alandon Tow Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2755F3E9-85B1-46CF-A69B-0D477EF8346A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7971CA69-1AC3-4670-982E-C9619292282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="1065" windowWidth="24720" windowHeight="14235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4724,10 +4724,10 @@
         <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H150" s="2">
-        <v>0</v>
+        <v>9.7569444444444448E-3</v>
       </c>
       <c r="I150" s="1">
         <v>46083.671643518515</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\DEN Camera System\Alandon Tow Service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7971CA69-1AC3-4670-982E-C9619292282C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB051DC-2D5E-46EE-8666-FED05831393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="45">
   <si>
     <t>Company Name</t>
   </si>
@@ -4811,10 +4811,10 @@
         <v>26</v>
       </c>
       <c r="G153" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H153" s="2">
-        <v>1.3888888888888889E-4</v>
+        <v>4.5717592592592589E-3</v>
       </c>
       <c r="I153" s="1">
         <v>46083.673032407409</v>
@@ -4827,10 +4827,32 @@
       </c>
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H154" s="2"/>
-      <c r="I154" s="1"/>
+      <c r="B154" t="s">
+        <v>32</v>
+      </c>
+      <c r="C154">
+        <v>2830</v>
+      </c>
+      <c r="D154" t="s">
+        <v>35</v>
+      </c>
+      <c r="F154" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" t="s">
+        <v>10</v>
+      </c>
+      <c r="H154" s="2">
+        <v>5.5092592592592589E-3</v>
+      </c>
+      <c r="I154" s="1">
+        <v>46083.673726851855</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
       <c r="K154" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
@@ -4838,10 +4860,10 @@
         <v>32</v>
       </c>
       <c r="C155">
-        <v>2830</v>
+        <v>2832</v>
       </c>
       <c r="D155" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F155" t="s">
         <v>26</v>
@@ -4850,13 +4872,13 @@
         <v>10</v>
       </c>
       <c r="H155" s="2">
-        <v>5.5092592592592589E-3</v>
+        <v>5.2199074074074075E-3</v>
       </c>
       <c r="I155" s="1">
         <v>46083.673726851855</v>
       </c>
       <c r="J155">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K155" t="s">
         <v>11</v>
@@ -4867,25 +4889,25 @@
         <v>32</v>
       </c>
       <c r="C156">
-        <v>2832</v>
+        <v>2825</v>
       </c>
       <c r="D156" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F156" t="s">
         <v>26</v>
       </c>
       <c r="G156" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H156" s="2">
-        <v>0</v>
+        <v>4.4444444444444444E-3</v>
       </c>
       <c r="I156" s="1">
-        <v>46083.673726851855</v>
+        <v>46083.674421296295</v>
       </c>
       <c r="J156">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K156" t="s">
         <v>11</v>
@@ -4896,10 +4918,10 @@
         <v>32</v>
       </c>
       <c r="C157">
-        <v>2825</v>
+        <v>2827</v>
       </c>
       <c r="D157" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F157" t="s">
         <v>26</v>
@@ -4911,43 +4933,18 @@
         <v>0</v>
       </c>
       <c r="I157" s="1">
-        <v>46083.674421296295</v>
+        <v>46083.675115740742</v>
       </c>
       <c r="J157">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K157" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B158" t="s">
-        <v>32</v>
-      </c>
-      <c r="C158">
-        <v>2827</v>
-      </c>
-      <c r="D158" t="s">
-        <v>41</v>
-      </c>
-      <c r="F158" t="s">
-        <v>26</v>
-      </c>
-      <c r="G158" t="s">
-        <v>13</v>
-      </c>
-      <c r="H158" s="2">
-        <v>0</v>
-      </c>
-      <c r="I158" s="1">
-        <v>46083.675115740742</v>
-      </c>
-      <c r="J158">
-        <v>3</v>
-      </c>
-      <c r="K158" t="s">
-        <v>11</v>
-      </c>
+      <c r="H158" s="2"/>
+      <c r="I158" s="1"/>
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H159" s="2"/>
@@ -27618,5 +27615,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB051DC-2D5E-46EE-8666-FED05831393F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0644A1-63ED-48FC-B75C-C49DCC737360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0644A1-63ED-48FC-B75C-C49DCC737360}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8BB0AF-AD3B-4719-8562-19E58CCCF59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>Austin Simms</t>
+  </si>
+  <si>
+    <t>Space Management for Commercial Vehicles</t>
   </si>
 </sst>
 </file>
@@ -4943,78 +4946,312 @@
       </c>
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H158" s="2"/>
-      <c r="I158" s="1"/>
+      <c r="B158" t="s">
+        <v>32</v>
+      </c>
+      <c r="C158">
+        <v>2919</v>
+      </c>
+      <c r="D158" t="s">
+        <v>39</v>
+      </c>
+      <c r="F158" t="s">
+        <v>45</v>
+      </c>
+      <c r="G158" t="s">
+        <v>10</v>
+      </c>
+      <c r="H158" s="2">
+        <v>1.3888888888888888E-2</v>
+      </c>
+      <c r="I158" s="1">
+        <v>46118.683217592596</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H159" s="2"/>
-      <c r="I159" s="1"/>
+      <c r="B159" t="s">
+        <v>32</v>
+      </c>
+      <c r="C159">
+        <v>2826</v>
+      </c>
+      <c r="D159" t="s">
+        <v>33</v>
+      </c>
+      <c r="F159" t="s">
+        <v>45</v>
+      </c>
+      <c r="G159" t="s">
+        <v>12</v>
+      </c>
+      <c r="H159" s="2">
+        <v>1.1574074074074075E-4</v>
+      </c>
+      <c r="I159" s="1">
+        <v>46118.683217592596</v>
+      </c>
+      <c r="J159">
+        <v>1</v>
+      </c>
+      <c r="K159" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H160" s="2"/>
       <c r="I160" s="1"/>
-    </row>
-    <row r="161" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H161" s="2"/>
-      <c r="I161" s="1"/>
-    </row>
-    <row r="162" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H162" s="2"/>
-      <c r="I162" s="1"/>
-    </row>
-    <row r="163" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H163" s="2"/>
-      <c r="I163" s="1"/>
-    </row>
-    <row r="164" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H164" s="2"/>
-      <c r="I164" s="1"/>
-    </row>
-    <row r="165" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H165" s="2"/>
-      <c r="I165" s="1"/>
-    </row>
-    <row r="166" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K160" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="161" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>32</v>
+      </c>
+      <c r="C161">
+        <v>3666</v>
+      </c>
+      <c r="D161" t="s">
+        <v>42</v>
+      </c>
+      <c r="F161" t="s">
+        <v>45</v>
+      </c>
+      <c r="G161" t="s">
+        <v>10</v>
+      </c>
+      <c r="H161" s="2">
+        <v>7.1875000000000003E-3</v>
+      </c>
+      <c r="I161" s="1">
+        <v>46118.683912037035</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>32</v>
+      </c>
+      <c r="C162">
+        <v>2828</v>
+      </c>
+      <c r="D162" t="s">
+        <v>34</v>
+      </c>
+      <c r="F162" t="s">
+        <v>45</v>
+      </c>
+      <c r="G162" t="s">
+        <v>13</v>
+      </c>
+      <c r="H162" s="2">
+        <v>0</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46118.683912037035</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>32</v>
+      </c>
+      <c r="C163">
+        <v>4883</v>
+      </c>
+      <c r="D163" t="s">
+        <v>43</v>
+      </c>
+      <c r="F163" t="s">
+        <v>45</v>
+      </c>
+      <c r="G163" t="s">
+        <v>10</v>
+      </c>
+      <c r="H163" s="2">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="I163" s="1">
+        <v>46118.684606481482</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>32</v>
+      </c>
+      <c r="C164">
+        <v>2830</v>
+      </c>
+      <c r="D164" t="s">
+        <v>35</v>
+      </c>
+      <c r="F164" t="s">
+        <v>45</v>
+      </c>
+      <c r="G164" t="s">
+        <v>10</v>
+      </c>
+      <c r="H164" s="2">
+        <v>8.1018518518518514E-3</v>
+      </c>
+      <c r="I164" s="1">
+        <v>46118.685300925928</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>32</v>
+      </c>
+      <c r="C165">
+        <v>2832</v>
+      </c>
+      <c r="D165" t="s">
+        <v>37</v>
+      </c>
+      <c r="F165" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165" t="s">
+        <v>12</v>
+      </c>
+      <c r="H165" s="2">
+        <v>2.9513888888888888E-3</v>
+      </c>
+      <c r="I165" s="1">
+        <v>46118.685300925928</v>
+      </c>
+      <c r="J165">
+        <v>1</v>
+      </c>
+      <c r="K165" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H166" s="2"/>
       <c r="I166" s="1"/>
-    </row>
-    <row r="167" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H167" s="2"/>
-      <c r="I167" s="1"/>
-    </row>
-    <row r="168" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H168" s="2"/>
-      <c r="I168" s="1"/>
-    </row>
-    <row r="169" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K166" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="167" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167">
+        <v>2825</v>
+      </c>
+      <c r="D167" t="s">
+        <v>38</v>
+      </c>
+      <c r="F167" t="s">
+        <v>45</v>
+      </c>
+      <c r="G167" t="s">
+        <v>13</v>
+      </c>
+      <c r="H167" s="2">
+        <v>0</v>
+      </c>
+      <c r="I167" s="1">
+        <v>46118.685995370368</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="168" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>32</v>
+      </c>
+      <c r="C168">
+        <v>2827</v>
+      </c>
+      <c r="D168" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168" t="s">
+        <v>12</v>
+      </c>
+      <c r="H168" s="2">
+        <v>4.9768518518518521E-3</v>
+      </c>
+      <c r="I168" s="1">
+        <v>46118.686689814815</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H169" s="2"/>
       <c r="I169" s="1"/>
-    </row>
-    <row r="170" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="K169" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H170" s="2"/>
       <c r="I170" s="1"/>
     </row>
-    <row r="171" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H171" s="2"/>
       <c r="I171" s="1"/>
     </row>
-    <row r="172" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H172" s="2"/>
       <c r="I172" s="1"/>
     </row>
-    <row r="173" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H173" s="2"/>
       <c r="I173" s="1"/>
     </row>
-    <row r="174" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H174" s="2"/>
       <c r="I174" s="1"/>
     </row>
-    <row r="175" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H175" s="2"/>
       <c r="I175" s="1"/>
     </row>
-    <row r="176" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H176" s="2"/>
       <c r="I176" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C8BB0AF-AD3B-4719-8562-19E58CCCF59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E328691-FEA4-4403-8D26-314D2C2AF611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5062,7 +5062,7 @@
         <v>46118.683912037035</v>
       </c>
       <c r="J162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K162" t="s">
         <v>11</v>
@@ -5185,7 +5185,7 @@
         <v>46118.685995370368</v>
       </c>
       <c r="J167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K167" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E328691-FEA4-4403-8D26-314D2C2AF611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E22FD95-0E4F-4CF8-9B1E-F01E34FA7035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -4988,10 +4988,10 @@
         <v>45</v>
       </c>
       <c r="G159" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H159" s="2">
-        <v>1.1574074074074075E-4</v>
+        <v>2.8935185185185184E-3</v>
       </c>
       <c r="I159" s="1">
         <v>46118.683217592596</v>
@@ -5004,10 +5004,32 @@
       </c>
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H160" s="2"/>
-      <c r="I160" s="1"/>
+      <c r="B160" t="s">
+        <v>32</v>
+      </c>
+      <c r="C160">
+        <v>3666</v>
+      </c>
+      <c r="D160" t="s">
+        <v>42</v>
+      </c>
+      <c r="F160" t="s">
+        <v>45</v>
+      </c>
+      <c r="G160" t="s">
+        <v>10</v>
+      </c>
+      <c r="H160" s="2">
+        <v>7.1875000000000003E-3</v>
+      </c>
+      <c r="I160" s="1">
+        <v>46118.683912037035</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
       <c r="K160" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
@@ -5015,10 +5037,10 @@
         <v>32</v>
       </c>
       <c r="C161">
-        <v>3666</v>
+        <v>2828</v>
       </c>
       <c r="D161" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F161" t="s">
         <v>45</v>
@@ -5027,13 +5049,13 @@
         <v>10</v>
       </c>
       <c r="H161" s="2">
-        <v>7.1875000000000003E-3</v>
+        <v>1.4155092592592592E-2</v>
       </c>
       <c r="I161" s="1">
         <v>46118.683912037035</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K161" t="s">
         <v>11</v>
@@ -5044,25 +5066,25 @@
         <v>32</v>
       </c>
       <c r="C162">
-        <v>2828</v>
+        <v>4883</v>
       </c>
       <c r="D162" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F162" t="s">
         <v>45</v>
       </c>
       <c r="G162" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H162" s="2">
+        <v>7.5115740740740742E-3</v>
+      </c>
+      <c r="I162" s="1">
+        <v>46118.684606481482</v>
+      </c>
+      <c r="J162">
         <v>0</v>
-      </c>
-      <c r="I162" s="1">
-        <v>46118.683912037035</v>
-      </c>
-      <c r="J162">
-        <v>2</v>
       </c>
       <c r="K162" t="s">
         <v>11</v>
@@ -5073,10 +5095,10 @@
         <v>32</v>
       </c>
       <c r="C163">
-        <v>4883</v>
+        <v>2830</v>
       </c>
       <c r="D163" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F163" t="s">
         <v>45</v>
@@ -5085,10 +5107,10 @@
         <v>10</v>
       </c>
       <c r="H163" s="2">
-        <v>7.5115740740740742E-3</v>
+        <v>8.1018518518518514E-3</v>
       </c>
       <c r="I163" s="1">
-        <v>46118.684606481482</v>
+        <v>46118.685300925928</v>
       </c>
       <c r="J163">
         <v>0</v>
@@ -5102,64 +5124,64 @@
         <v>32</v>
       </c>
       <c r="C164">
-        <v>2830</v>
+        <v>2832</v>
       </c>
       <c r="D164" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F164" t="s">
         <v>45</v>
       </c>
       <c r="G164" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H164" s="2">
-        <v>8.1018518518518514E-3</v>
+        <v>2.9513888888888888E-3</v>
       </c>
       <c r="I164" s="1">
         <v>46118.685300925928</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B165" t="s">
+      <c r="H165" s="2"/>
+      <c r="I165" s="1"/>
+      <c r="K165" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
         <v>32</v>
       </c>
-      <c r="C165">
-        <v>2832</v>
-      </c>
-      <c r="D165" t="s">
-        <v>37</v>
-      </c>
-      <c r="F165" t="s">
+      <c r="C166">
+        <v>2825</v>
+      </c>
+      <c r="D166" t="s">
+        <v>38</v>
+      </c>
+      <c r="F166" t="s">
         <v>45</v>
       </c>
-      <c r="G165" t="s">
-        <v>12</v>
-      </c>
-      <c r="H165" s="2">
-        <v>2.9513888888888888E-3</v>
-      </c>
-      <c r="I165" s="1">
-        <v>46118.685300925928</v>
-      </c>
-      <c r="J165">
-        <v>1</v>
-      </c>
-      <c r="K165" t="s">
+      <c r="G166" t="s">
+        <v>10</v>
+      </c>
+      <c r="H166" s="2">
+        <v>7.6388888888888886E-3</v>
+      </c>
+      <c r="I166" s="1">
+        <v>46118.685995370368</v>
+      </c>
+      <c r="J166">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="166" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H166" s="2"/>
-      <c r="I166" s="1"/>
-      <c r="K166" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
@@ -5167,65 +5189,40 @@
         <v>32</v>
       </c>
       <c r="C167">
-        <v>2825</v>
+        <v>2827</v>
       </c>
       <c r="D167" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F167" t="s">
         <v>45</v>
       </c>
       <c r="G167" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H167" s="2">
+        <v>4.9768518518518521E-3</v>
+      </c>
+      <c r="I167" s="1">
+        <v>46118.686689814815</v>
+      </c>
+      <c r="J167">
         <v>0</v>
-      </c>
-      <c r="I167" s="1">
-        <v>46118.685995370368</v>
-      </c>
-      <c r="J167">
-        <v>2</v>
       </c>
       <c r="K167" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B168" t="s">
-        <v>32</v>
-      </c>
-      <c r="C168">
-        <v>2827</v>
-      </c>
-      <c r="D168" t="s">
-        <v>41</v>
-      </c>
-      <c r="F168" t="s">
-        <v>45</v>
-      </c>
-      <c r="G168" t="s">
-        <v>12</v>
-      </c>
-      <c r="H168" s="2">
-        <v>4.9768518518518521E-3</v>
-      </c>
-      <c r="I168" s="1">
-        <v>46118.686689814815</v>
-      </c>
-      <c r="J168">
-        <v>0</v>
-      </c>
+      <c r="H168" s="2"/>
+      <c r="I168" s="1"/>
       <c r="K168" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H169" s="2"/>
       <c r="I169" s="1"/>
-      <c r="K169" t="s">
-        <v>27</v>
-      </c>
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H170" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E22FD95-0E4F-4CF8-9B1E-F01E34FA7035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66A8DE-09DC-4EE5-A8EE-367156D3E544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="46">
   <si>
     <t>Company Name</t>
   </si>
@@ -5221,98 +5221,326 @@
       </c>
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H169" s="2"/>
-      <c r="I169" s="1"/>
+      <c r="B169" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169">
+        <v>2919</v>
+      </c>
+      <c r="D169" t="s">
+        <v>39</v>
+      </c>
+      <c r="F169" t="s">
+        <v>20</v>
+      </c>
+      <c r="G169" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" s="2">
+        <v>0</v>
+      </c>
+      <c r="I169" s="1">
+        <v>46146.58761574074</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="170" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H170" s="2"/>
-      <c r="I170" s="1"/>
+      <c r="B170" t="s">
+        <v>32</v>
+      </c>
+      <c r="C170">
+        <v>2826</v>
+      </c>
+      <c r="D170" t="s">
+        <v>33</v>
+      </c>
+      <c r="F170" t="s">
+        <v>20</v>
+      </c>
+      <c r="G170" t="s">
+        <v>10</v>
+      </c>
+      <c r="H170" s="2">
+        <v>3.2175925925925926E-3</v>
+      </c>
+      <c r="I170" s="1">
+        <v>46146.588310185187</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H171" s="2"/>
-      <c r="I171" s="1"/>
+      <c r="B171" t="s">
+        <v>32</v>
+      </c>
+      <c r="C171">
+        <v>3666</v>
+      </c>
+      <c r="D171" t="s">
+        <v>42</v>
+      </c>
+      <c r="F171" t="s">
+        <v>20</v>
+      </c>
+      <c r="G171" t="s">
+        <v>10</v>
+      </c>
+      <c r="H171" s="2">
+        <v>6.9560185185185185E-3</v>
+      </c>
+      <c r="I171" s="1">
+        <v>46146.588310185187</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H172" s="2"/>
-      <c r="I172" s="1"/>
+      <c r="B172" t="s">
+        <v>32</v>
+      </c>
+      <c r="C172">
+        <v>2828</v>
+      </c>
+      <c r="D172" t="s">
+        <v>34</v>
+      </c>
+      <c r="F172" t="s">
+        <v>20</v>
+      </c>
+      <c r="G172" t="s">
+        <v>13</v>
+      </c>
+      <c r="H172" s="2">
+        <v>0</v>
+      </c>
+      <c r="I172" s="1">
+        <v>46146.589004629626</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H173" s="2"/>
-      <c r="I173" s="1"/>
+      <c r="B173" t="s">
+        <v>32</v>
+      </c>
+      <c r="C173">
+        <v>4883</v>
+      </c>
+      <c r="D173" t="s">
+        <v>43</v>
+      </c>
+      <c r="F173" t="s">
+        <v>20</v>
+      </c>
+      <c r="G173" t="s">
+        <v>13</v>
+      </c>
+      <c r="H173" s="2">
+        <v>0</v>
+      </c>
+      <c r="I173" s="1">
+        <v>46146.589699074073</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H174" s="2"/>
-      <c r="I174" s="1"/>
+      <c r="B174" t="s">
+        <v>32</v>
+      </c>
+      <c r="C174">
+        <v>2830</v>
+      </c>
+      <c r="D174" t="s">
+        <v>35</v>
+      </c>
+      <c r="F174" t="s">
+        <v>20</v>
+      </c>
+      <c r="G174" t="s">
+        <v>12</v>
+      </c>
+      <c r="H174" s="2">
+        <v>6.5162037037037037E-3</v>
+      </c>
+      <c r="I174" s="1">
+        <v>46146.589699074073</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H175" s="2"/>
       <c r="I175" s="1"/>
+      <c r="K175" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H176" s="2"/>
-      <c r="I176" s="1"/>
-    </row>
-    <row r="177" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H177" s="2"/>
-      <c r="I177" s="1"/>
-    </row>
-    <row r="178" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H178" s="2"/>
-      <c r="I178" s="1"/>
-    </row>
-    <row r="179" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176">
+        <v>2832</v>
+      </c>
+      <c r="D176" t="s">
+        <v>37</v>
+      </c>
+      <c r="F176" t="s">
+        <v>20</v>
+      </c>
+      <c r="G176" t="s">
+        <v>13</v>
+      </c>
+      <c r="H176" s="2">
+        <v>0</v>
+      </c>
+      <c r="I176" s="1">
+        <v>46146.59039351852</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="177" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>32</v>
+      </c>
+      <c r="C177">
+        <v>2825</v>
+      </c>
+      <c r="D177" t="s">
+        <v>38</v>
+      </c>
+      <c r="F177" t="s">
+        <v>20</v>
+      </c>
+      <c r="G177" t="s">
+        <v>13</v>
+      </c>
+      <c r="H177" s="2">
+        <v>0</v>
+      </c>
+      <c r="I177" s="1">
+        <v>46146.591087962966</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>32</v>
+      </c>
+      <c r="C178">
+        <v>2827</v>
+      </c>
+      <c r="D178" t="s">
+        <v>41</v>
+      </c>
+      <c r="F178" t="s">
+        <v>20</v>
+      </c>
+      <c r="G178" t="s">
+        <v>10</v>
+      </c>
+      <c r="H178" s="2">
+        <v>4.8495370370370368E-3</v>
+      </c>
+      <c r="I178" s="1">
+        <v>46146.591087962966</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H179" s="2"/>
       <c r="I179" s="1"/>
     </row>
-    <row r="180" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H180" s="2"/>
       <c r="I180" s="1"/>
     </row>
-    <row r="181" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H181" s="2"/>
       <c r="I181" s="1"/>
     </row>
-    <row r="182" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H182" s="2"/>
       <c r="I182" s="1"/>
     </row>
-    <row r="183" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H183" s="2"/>
       <c r="I183" s="1"/>
     </row>
-    <row r="184" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H184" s="2"/>
       <c r="I184" s="1"/>
     </row>
-    <row r="185" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H185" s="2"/>
       <c r="I185" s="1"/>
     </row>
-    <row r="186" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H186" s="2"/>
       <c r="I186" s="1"/>
     </row>
-    <row r="187" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H187" s="2"/>
       <c r="I187" s="1"/>
     </row>
-    <row r="188" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H188" s="2"/>
       <c r="I188" s="1"/>
     </row>
-    <row r="189" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H189" s="2"/>
       <c r="I189" s="1"/>
     </row>
-    <row r="190" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H190" s="2"/>
       <c r="I190" s="1"/>
     </row>
-    <row r="191" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H191" s="2"/>
       <c r="I191" s="1"/>
     </row>
-    <row r="192" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H192" s="2"/>
       <c r="I192" s="1"/>
     </row>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E66A8DE-09DC-4EE5-A8EE-367156D3E544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A18C51-B515-4776-8A6E-F6B1165C4E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5350,10 +5350,10 @@
         <v>20</v>
       </c>
       <c r="G173" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H173" s="2">
-        <v>0</v>
+        <v>4.2245370370370371E-3</v>
       </c>
       <c r="I173" s="1">
         <v>46146.589699074073</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Dual Reports\Alandon Tow Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8162E3-E86A-48FD-85C2-3FEF222CB613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ECB59C7-6E80-4076-B953-D8DA4DE60CC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -5243,7 +5243,7 @@
         <v>46146.58761574074</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K169" t="s">
         <v>11</v>
@@ -5330,7 +5330,7 @@
         <v>46146.589004629626</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K172" t="s">
         <v>11</v>
@@ -5415,16 +5415,16 @@
         <v>20</v>
       </c>
       <c r="G176" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H176" s="2">
-        <v>0</v>
+        <v>4.7685185185185183E-3</v>
       </c>
       <c r="I176" s="1">
         <v>46146.59039351852</v>
       </c>
       <c r="J176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K176" t="s">
         <v>11</v>
@@ -5453,7 +5453,7 @@
         <v>46146.591087962966</v>
       </c>
       <c r="J177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Alandon Tow Service- TS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Alandon-Tow-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DF995F-D9BF-4BC1-80D7-9B78DE60BDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA214BD-E65F-4A9F-B193-CF81ED6BD128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1215" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Alandon-Tow-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46594EB2-B0CC-417E-8E46-363A833F9794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7499817-B639-4682-B492-8E2A906087B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -30659,5 +30659,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Alandon-Tow-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F342DA2-E712-483A-BDB5-595142D34B18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3B71843-93CC-4D64-8F32-9F6FA8FB105F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -556,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -571,39 +571,39 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>31</v>
       </c>
@@ -632,7 +632,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>31</v>
       </c>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>31</v>
       </c>
@@ -690,7 +690,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>31</v>
       </c>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>31</v>
       </c>
@@ -748,7 +748,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>31</v>
       </c>
@@ -777,7 +777,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -806,7 +806,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>31</v>
       </c>
@@ -835,7 +835,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>31</v>
       </c>
@@ -864,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>31</v>
       </c>
@@ -893,7 +893,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>31</v>
       </c>
@@ -922,7 +922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>31</v>
       </c>
@@ -951,7 +951,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>31</v>
       </c>
@@ -980,7 +980,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>31</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H16" s="2"/>
       <c r="I16" s="1"/>
       <c r="J16" s="2"/>
@@ -6157,10 +6157,10 @@
         <v>30</v>
       </c>
       <c r="G201" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H201" s="2">
-        <v>0</v>
+        <v>5.8912037037037041E-3</v>
       </c>
       <c r="I201" s="1">
         <v>46237.632870370369</v>
@@ -6186,10 +6186,10 @@
         <v>30</v>
       </c>
       <c r="G202" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H202" s="2">
-        <v>0</v>
+        <v>7.0949074074074074E-3</v>
       </c>
       <c r="I202" s="1">
         <v>46237.633564814816</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Alandon-Tow-Service\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57887A03-9CB0-4D41-9594-5AA0496D83BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6127F1D-2188-441A-9AB3-C1F6A95B2DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
